--- a/TheRunics_Data/StreamingAssets/runics.xlsx
+++ b/TheRunics_Data/StreamingAssets/runics.xlsx
@@ -4997,7 +4997,7 @@
         <v>4</v>
       </c>
       <c r="G195">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H195">
         <v>-1</v>
@@ -5072,7 +5072,7 @@
         <v>4</v>
       </c>
       <c r="G199">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H199">
         <v>-1</v>
@@ -5147,10 +5147,10 @@
         <v>3</v>
       </c>
       <c r="G203">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H203">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="205" spans="3:13">
@@ -5222,7 +5222,7 @@
         <v>5</v>
       </c>
       <c r="G207">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H207">
         <v>20</v>
@@ -5297,7 +5297,7 @@
         <v>3</v>
       </c>
       <c r="G211">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H211">
         <v>-1</v>
@@ -5378,7 +5378,7 @@
         <v>3</v>
       </c>
       <c r="G215">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H215">
         <v>-1</v>
